--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -6558,7 +6558,7 @@
         <v>46235</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>17.1387</v>
+        <v>17.1408</v>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6548,64 +6548,6 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>Ago 26</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C109" s="9" t="n">
-        <v>17.1408</v>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>-8.1%</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Pesos por dólar</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="I109" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr">
-        <is>
-          <t>Banco de México (SIE)</t>
-        </is>
-      </c>
-      <c r="K109" s="7" t="inlineStr">
-        <is>
-          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
-        </is>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:L3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3943,6 +3943,39 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>17.0427</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2183"/>
+  <dimension ref="A1:G2184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68060,6 +68060,37 @@
         </is>
       </c>
     </row>
+    <row r="2184">
+      <c r="A2184" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2184" s="4" t="n"/>
+      <c r="C2184" s="5" t="n">
+        <v>17.0147</v>
+      </c>
+      <c r="D2184" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2184" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="F2184" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2184" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2184"/>
+  <dimension ref="A1:G2185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68091,6 +68091,37 @@
         </is>
       </c>
     </row>
+    <row r="2185">
+      <c r="A2185" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2185" s="4" t="n"/>
+      <c r="C2185" s="7" t="n">
+        <v>16.9755</v>
+      </c>
+      <c r="D2185" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2185" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2185" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2185" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2185"/>
+  <dimension ref="A1:G2186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68122,6 +68122,37 @@
         </is>
       </c>
     </row>
+    <row r="2186">
+      <c r="A2186" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B2186" s="4" t="n"/>
+      <c r="C2186" s="5" t="n">
+        <v>16.9852</v>
+      </c>
+      <c r="D2186" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2186" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="F2186" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2186" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2187"/>
+  <dimension ref="A1:G2188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68184,6 +68184,37 @@
         </is>
       </c>
     </row>
+    <row r="2188">
+      <c r="A2188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B2188" s="4" t="n"/>
+      <c r="C2188" s="5" t="n">
+        <v>16.8748</v>
+      </c>
+      <c r="D2188" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2188" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2188" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2188" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2188"/>
+  <dimension ref="A1:G2189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68215,6 +68215,37 @@
         </is>
       </c>
     </row>
+    <row r="2189">
+      <c r="A2189" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2189" s="4" t="n"/>
+      <c r="C2189" s="7" t="n">
+        <v>16.9237</v>
+      </c>
+      <c r="D2189" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2189" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2189" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2189" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2189"/>
+  <dimension ref="A1:G2190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68246,6 +68246,37 @@
         </is>
       </c>
     </row>
+    <row r="2190">
+      <c r="A2190" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2190" s="4" t="n"/>
+      <c r="C2190" s="5" t="n">
+        <v>16.9202</v>
+      </c>
+      <c r="D2190" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2190" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2190" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2190" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2190"/>
+  <dimension ref="A1:G2191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68277,6 +68277,37 @@
         </is>
       </c>
     </row>
+    <row r="2191">
+      <c r="A2191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2191" s="4" t="n"/>
+      <c r="C2191" s="7" t="n">
+        <v>16.8947</v>
+      </c>
+      <c r="D2191" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2191" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2191" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2191" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2191"/>
+  <dimension ref="A1:G2192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68308,6 +68308,37 @@
         </is>
       </c>
     </row>
+    <row r="2192">
+      <c r="A2192" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2192" s="4" t="n"/>
+      <c r="C2192" s="5" t="n">
+        <v>16.9722</v>
+      </c>
+      <c r="D2192" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2192" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2192" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2192" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2192"/>
+  <dimension ref="A1:G2193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68339,6 +68339,37 @@
         </is>
       </c>
     </row>
+    <row r="2193">
+      <c r="A2193" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2193" s="4" t="n"/>
+      <c r="C2193" s="7" t="n">
+        <v>16.9707</v>
+      </c>
+      <c r="D2193" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2193" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2193" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2193" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
